--- a/data_extactor/batch_10_fa/batch_0039_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0039_fa.xlsx
@@ -493,42 +493,42 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Producers and Directors (تهیه‌کنندگان و کارگردانان)</t>
+          <t>تهیه‌کنندگان و کارگردانان (Producers and Directors)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Artistic Director | Director | Executive Producer | Multimedia Producer | News Producer | Producer | Production Director | Radio Producer | Television News Producer (TV News Producer) | Television Producer (TV Producer)</t>
+          <t>مدیر هنری | کارگردان | تهیه‌کننده اجرایی | تهیه‌کننده چندرسانه‌ای | تهیه‌کننده خبر | تهیه‌کننده | مدیر تولید | تهیه‌کننده رادیو | تهیه‌کننده اخبار تلویزیونی (TV News Producer) | تهیه‌کننده تلویزیونی (TV Producer)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>AP ENPS | Adobe Acrobat | Adobe ActionScript | Adobe After Effects | Adobe Audition | Adobe Creative Cloud software | Adobe Dreamweaver | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | Adobe Premiere Pro | Airtable | Apple Final Cut Pro | Asana | Atlassian Confluence | Atlassian JIRA | Avid Digidesign Pro Tools | Avid Technology Media Composer | Avid Technology NewsCutter | Avid Technology Pro Tools | Avid Technology iNEWS | نرم‌افزار وبلاگ‌نویسی | Broadcast Electronics AudioVAULT FleX | Canva | Cascading style sheets CSS | Chyron CAMIO | سیستم‌های مدیریت محتوا CMS | Drupal | Eko | نرم‌افزار ایمیل | Extensible markup language XML | FaceTime | Facebook | Google Ads | Google Analytics | Google Docs | Google Drive | Google Gmail | نرم‌افزار Google Workspace | نرم‌افزار ایجاد گرافیک | Grass Valley EDIUS | Hypertext markup language HTML | Instagram | JavaScript | LinkedIn | نرم‌افزار پخش زنده | MAGIX Software Sound Forge | Magix Vegas Pro | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Publisher | Microsoft Teams | Microsoft Visio | Microsoft Windows | Microsoft Word | PHP | Pinterest | Ross Video Xpression | Screencastify | نرم‌افزار اسکریپت‌نویسی | Slack | Snapchat | سایت‌های رسانه‌های اجتماعی | TikTok | Twitter | نرم‌افزار ویرایش ویدیو | نرم‌افزار سیستم مدیریت محتوای وب CMS | WideOrbit | WordPress | YouTube | Zoom</t>
+          <t>AP ENPS | Adobe Acrobat | Adobe ActionScript | Adobe After Effects | Adobe Audition | نرم‌افزار Adobe Creative Cloud | Adobe Dreamweaver | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | Adobe Premiere Pro | Airtable | Apple Final Cut Pro | Asana | Atlassian Confluence | Atlassian JIRA | Avid Digidesign Pro Tools | Avid Technology Media Composer | Avid Technology NewsCutter | Avid Technology Pro Tools | Avid Technology iNEWS | نرم‌افزار وبلاگ‌نویسی | Broadcast Electronics AudioVAULT FleX | Canva | برگه‌های سبک آبشاری CSS | Chyron CAMIO | سیستم‌های مدیریت محتوا CMS | Drupal | Eko | نرم‌افزار ایمیل | زبان نشانه‌گذاری توسعه‌پذیر XML | FaceTime | Facebook | Google Ads | Google Analytics | Google Docs | Google Drive | Google Gmail | نرم‌افزار Google Workspace | نرم‌افزار ایجاد گرافیک | Grass Valley EDIUS | زبان نشانه‌گذاری ابرمتن HTML | Instagram | JavaScript | LinkedIn | نرم‌افزار پخش زنده | MAGIX Software Sound Forge | Magix Vegas Pro | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Publisher | Microsoft Teams | Microsoft Visio | Microsoft Windows | Microsoft Word | PHP | Pinterest | Ross Video Xpression | Screencastify | نرم‌افزار اسکریپت‌نویسی | Slack | Snapchat | سایت‌های رسانه‌های اجتماعی | TikTok | Twitter | نرم‌افزار ویرایش ویدیو | نرم‌افزار سیستم مدیریت محتوای وب CMS | WideOrbit | WordPress | YouTube | Zoom</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | نظارت | تفکر انتقادی | صحبت کردن | درک مطلب | نوشتن | یادگیری فعال | استراتژی‌های یادگیری</t>
+          <t>گوش دادن فعال | نظارت | تفکر انتقادی | سخن گفتن | درک مطلب | نگارش | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ارتباطات و رسانه | زبان انگلیسی | مخابرات | کامپیوتر و الکترونیک | مدیریت و اداره | خدمات مشتری و شخصی</t>
+          <t>ارتباطات و رسانه | زبان انگلیسی | مخابرات | رایانه و الکترونیک | مدیریت و اداره | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | استدلال قیاسی | حساسیت به مسئله | وضوح گفتار | درک نوشتاری | بیان نوشتاری | خلاقیت | نظم‌دهی اطلاعات | دید نزدیک | تشخیص گفتار | استدلال استقرایی | انعطاف‌پذیری دسته‌بندی | تجسم | دید دور | روانی ایده‌ها | انعطاف‌پذیری بستار | اشتراک زمانی | توجه انتخابی | سرعت بستار | سرعت ادراکی</t>
+          <t>بیان شفاهی | درک شفاهی | استدلال قیاسی | حساسیت به مسئله | وضوح گفتار | درک کتبی | بیان کتبی | اصالت | ترتیب‌دهی اطلاعات | بینایی نزدیک | تشخیص گفتار | استدلال استقرایی | انعطاف‌پذیری دسته‌بندی | تجسم | بینایی دور | روانی ایده‌ها | انعطاف‌پذیری بستار | تقسیم توجه | توجه انتخابی | سرعت بستار | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>ایمیل | کار با یا مشارکت در یک گروه کاری یا تیم | مکالمات تلفنی | تماس با دیگران | تناوب تصمیم‌گیری | بحث‌های رودررو با افراد و درون تیم‌ها | تأثیر تصمیمات بر همکاران یا نتایج شرکت | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | فشار زمانی | محیط داخلی، دارای کنترل محیطی | آزادی در تصمیم‌گیری | نتایج کاری و خروجی‌های سایر کارکنان | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای نشستن | اهمیت دقیق یا صحیح بودن | سطح رقابت | تعامل با مشتریان خارجی یا عموم مردم</t>
+          <t>ایمیل | کار با یا مشارکت در یک گروه کاری یا تیم | مکالمات تلفنی | ارتباط با دیگران | فراوانی تصمیم‌گیری | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تأثیر تصمیمات بر همکاران یا نتایج شرکت | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فشار زمانی | محیط داخلی، دارای کنترل شرایط محیطی | آزادی در تصمیم‌گیری | پیامدهای کاری و نتایج سایر کارکنان | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای نشستن | اهمیت دقیق یا درست بودن | سطح رقابت | تعامل با مشتریان خارجی یا عموم مردم</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>بازیگران | مدیران هنری | تکنسین‌های صوتی و تصویری | گویندگان پخش و دی‌جی‌های رادیو | اپراتورهای دوربین، تلویزیون، ویدیو و فیلم | ویراستاران | ویراستاران فیلم و ویدیو | طراحان گرافیک | مدیران برنامه‌ریزی رسانه | مدیران/کارگردانان فنی رسانه | مدیران موسیقی و آهنگسازان | تحلیلگران اخبار، گزارشگران و روزنامه‌نگاران | شاعران، ترانه‌سرایان و نویسندگان خلاق | متخصصان مدیریت پروژه | متخصصان روابط عمومی | تکنسین‌های مهندسی صدا | هنرمندان جلوه‌های ویژه و انیماتورها | مدیران استعداد | طراحان بازی‌های ویدیویی | نویسندگان و مؤلفان</t>
+          <t>بازیگران | مدیران هنری | تکنسین‌های صوتی و تصویری | گویندگان رادیو و تلویزیون و دی‌جی‌های رادیو | اپراتورهای دوربین، تلویزیون، ویدئو و فیلم | ویراستاران | تدوینگران فیلم و ویدئو | طراحان گرافیک | مدیران برنامه‌ریزی رسانه | مدیران/کارگردانان فنی رسانه | مدیران موسیقی و آهنگسازان | تحلیلگران اخبار، گزارشگران و روزنامه‌نگاران | شاعران، ترانه‌سرایان و نویسندگان خلاق | متخصصان مدیریت پروژه | متخصصان روابط عمومی | تکنسین‌های مهندسی صدا | هنرمندان جلوه‌های ویژه و انیماتورها | مدیران استعداد | طراحان بازی‌های ویدئویی | نویسندگان و مؤلفان</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -550,42 +550,42 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Media Programming Directors (مدیران برنامه‌ریزی رسانه)</t>
+          <t>مدیران برنامه‌ریزی رسانه (Media Programming Directors)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Broadcast Content Manager | News Director | Newscast Director | Production Director | Program Coordinator | Program Director (PD) | Program Manager | Programming Director | Station Manager | TV Program Director (Television Program Director)</t>
+          <t>مدیر محتوای پخش | مدیر اخبار | کارگردان بخش خبری | مدیر تولید | هماهنگ‌کننده برنامه | مدیر ارشد برنامه (PD) | مدیر برنامه | مدیر برنامه‌سازی | مدیر ایستگاه | مدیر برنامه تلویزیونی (TV Program Director)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Adobe Acrobat | نرم‌افزار Adobe Creative Cloud | Adobe Photoshop | Apple Final Cut Pro | نرم‌افزار ردیابی متقاضی | Avid Technology iNEWS | Broadcast Electronics AudioVAULT FleX | سیستم‌های مدیریت محتوا CMS | نرم‌افزار ایمیل | Facebook | FileMaker Pro | Google Analytics | Hypertext markup language HTML | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft SQL Server | Microsoft SharePoint | Microsoft Word | نرم‌افزار زمان‌بندی موسیقی | RCS GSelector | پایگاه‌های داده زمان‌بندی | TikTok | Twitter | نرم‌افزار مرورگر وب</t>
+          <t>Adobe Acrobat | نرم‌افزار Adobe Creative Cloud | Adobe Photoshop | Apple Final Cut Pro | نرم‌افزار ردیابی متقاضی | Avid Technology iNEWS | Broadcast Electronics AudioVAULT FleX | سیستم‌های مدیریت محتوا CMS | نرم‌افزار ایمیل | Facebook | FileMaker Pro | Google Analytics | زبان نشانه‌گذاری ابرمتن HTML | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft SQL Server | Microsoft SharePoint | Microsoft Word | نرم‌افزار زمان‌بندی موسیقی | RCS GSelector | پایگاه‌های داده زمان‌بندی | TikTok | Twitter | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>صحبت کردن | درک مطلب | تفکر انتقادی | یادگیری فعال | نظارت | گوش دادن فعال | نوشتن | استراتژی‌های یادگیری</t>
+          <t>سخن گفتن | درک مطلب | تفکر انتقادی | یادگیری فعال | نظارت | گوش دادن فعال | نگارش | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ارتباطات و رسانه | کامپیوتر و الکترونیک | زبان انگلیسی | مدیریت و اداره | مخابرات | خدمات مشتری و شخصی | فروش و بازاریابی | مهندسی و فناوری | اداری | پرسنل و منابع انسانی | آموزش و پرورش | تولید و پردازش | ریاضیات</t>
+          <t>ارتباطات و رسانه | رایانه و الکترونیک | زبان انگلیسی | مدیریت و اداره | مخابرات | خدمات مشتری و شخصی | فروش و بازاریابی | مهندسی و فناوری | اداری | پرسنل و منابع انسانی | آموزش و پرورش | تولید و فرآوری | ریاضیات</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | درک نوشتاری | بیان نوشتاری | حساسیت به مسئله | روانی ایده‌ها | وضوح گفتار | استدلال قیاسی | دید نزدیک | تشخیص گفتار | خلاقیت | نظم‌دهی اطلاعات | استدلال استقرایی | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | دید دور | اشتراک زمانی</t>
+          <t>درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | حساسیت به مسئله | روانی ایده‌ها | وضوح گفتار | استدلال قیاسی | بینایی نزدیک | تشخیص گفتار | اصالت | ترتیب‌دهی اطلاعات | استدلال استقرایی | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | بینایی دور | تقسیم توجه</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>ایمیل | تماس با دیگران | اهمیت دقیق یا صحیح بودن | بحث‌های رودررو با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل محیطی | مکالمات تلفنی | تناوب تصمیم‌گیری | صرف زمان برای نشستن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | فشار زمانی | تعامل با مشتریان خارجی یا عموم مردم | نتایج کاری و خروجی‌های سایر کارکنان | اهمیت تکرار وظایف مشابه | صرف زمان برای استفاده از دستان جهت کار با، کنترل یا احساس اشیاء، ابزارها یا کنترل‌ها</t>
+          <t>ایمیل | ارتباط با دیگران | اهمیت دقیق یا درست بودن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | مکالمات تلفنی | فراوانی تصمیم‌گیری | صرف زمان برای نشستن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | فشار زمانی | تعامل با مشتریان خارجی یا عموم مردم | پیامدهای کاری و نتایج سایر کارکنان | اهمیت تکرار وظایف یکسان | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>مدیران هنری | گویندگان پخش و دی‌جی‌های رادیو | مدیران ارشد اجرایی | مدیران، فعالیت‌های مذهبی و آموزش | منشی‌های اجرایی و دستیاران اداری اجرایی | سرپرستان خط اول کارکنان سرگرمی و تفریحی، به جز خدمات قمار | سرپرستان خط اول کارکنان فروش غیرخرده‌فروشی | سرپرستان خط اول کارکنان پشتیبانی اداری و دفتری | مدیران عمومی و عملیاتی | مدیران پروژه فناوری اطلاعات | هماهنگ‌کنندگان آموزشی | کتابداران و متخصصان مجموعه‌های رسانه‌ای | تحلیلگران مدیریت | مدیران/کارگردانان فنی رسانه | تهیه‌کنندگان و کارگردانان | متخصصان مدیریت پروژه | مدیران روابط عمومی | متخصصان روابط عمومی | مدیران استعداد | مدیران آموزش و توسعه</t>
+          <t>مدیران هنری | گویندگان رادیو و تلویزیون و دی‌جی‌های رادیو | مدیران ارشد اجرایی | مدیران، فعالیت‌ها و آموزش‌های مذهبی | منشی‌های اجرایی و دستیاران اداری اجرایی | سرپرستان خط اول کارگران سرگرمی و تفریح، به جز خدمات قمار | سرپرستان رده اول کارکنان فروش غیرخرده‌فروشی | سرپرستان خط اول کارکنان دفتری و پشتیبانی اداری | مدیران عمومی و عملیات | مدیران پروژه فناوری اطلاعات | هماهنگ‌کنندگان آموزشی | کتابداران و متخصصان مجموعه‌های رسانه‌ای | تحلیل‌گران مدیریت | مدیران/کارگردانان فنی رسانه | تهیه‌کنندگان و کارگردانان | متخصصان مدیریت پروژه | مدیران روابط عمومی | متخصصان روابط عمومی | مدیران استعداد | مدیران آموزش و توسعه</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -607,12 +607,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Talent Directors (مدیران استعداد)</t>
+          <t>مدیران استعداد (Talent Directors)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Artistic Director | Casting Agent | Casting Coordinator | Casting Director | Extras Casting Director | Model Booker | Talent Producer | Talent Scout</t>
+          <t>مدیر هنری | نماینده انتخاب بازیگر | هماهنگ‌کننده انتخاب بازیگر | مدیر انتخاب بازیگر | مدیر انتخاب سیاهی‌لشکر | هماهنگ‌کننده قرارداد مدل‌ها | تهیه‌کننده استعدادیابی | استعدادیاب</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>صحبت کردن | گوش دادن فعال | درک مطلب | تفکر انتقادی | نظارت | نوشتن | یادگیری فعال</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | نظارت | نگارش | یادگیری فعال</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -632,17 +632,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | درک نوشتاری | استدلال استقرایی | وضوح گفتار | بیان نوشتاری | خلاقیت | استدلال قیاسی | تشخیص گفتار | دید نزدیک | حساسیت به مسئله | روانی ایده‌ها | نظم‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | دید دور</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | استدلال استقرایی | وضوح گفتار | بیان کتبی | اصالت | استدلال قیاسی | تشخیص گفتار | بینایی نزدیک | حساسیت به مسئله | روانی ایده‌ها | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | بینایی دور</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | تماس با دیگران | تعیین وظایف، اولویت‌ها و اهداف | تأثیر تصمیمات بر همکاران یا نتایج شرکت | محیط داخلی، دارای کنترل محیطی | بحث‌های رودررو با افراد و درون تیم‌ها | آزادی در تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | نتایج کاری و خروجی‌های سایر کارکنان | تعامل با مشتریان خارجی یا عموم مردم | صرف زمان برای نشستن | تناوب تصمیم‌گیری | نامه‌ها و یادداشت‌های کتبی | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | فشار زمانی</t>
+          <t>ایمیل | مکالمات تلفنی | ارتباط با دیگران | تعیین وظایف، اولویت‌ها و اهداف | تأثیر تصمیمات بر همکاران یا نتایج شرکت | محیط داخلی، دارای کنترل شرایط محیطی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | آزادی در تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | پیامدهای کاری و نتایج سایر کارکنان | تعامل با مشتریان خارجی یا عموم مردم | صرف زمان برای نشستن | فراوانی تصمیم‌گیری | نامه‌ها و یادداشت‌های کتبی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فشار زمانی</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>بازیگران | مدیران تبلیغات و ترویج | نمایندگان و مدیران تجاری هنرمندان، مجریان و ورزشکاران | مدیران هنری | گویندگان پخش و دی‌جی‌های رادیو | طراحان رقص | مدیران، فعالیت‌های مذهبی و آموزش | متخصصان منابع انسانی | هماهنگ‌کنندگان آموزشی | مدیران برنامه‌ریزی رسانه | مدیران/کارگردانان فنی رسانه | برنامه‌ریزان جلسات، کنوانسیون‌ها و رویدادها | مدیران موسیقی و آهنگسازان | نوازندگان و خوانندگان | شاعران، ترانه‌سرایان و نویسندگان خلاق | تهیه‌کنندگان و کارگردانان | متخصصان روابط عمومی | مدیران آموزش و توسعه | متخصصان آموزش و توسعه | نویسندگان و مؤلفان</t>
+          <t>بازیگران | مدیران تبلیغات و ترویج | نمایندگان و مدیران تجاری هنرمندان، اجراکنندگان و ورزشکاران | مدیران هنری | گویندگان رادیو و تلویزیون و دی‌جی‌های رادیو | طراحان رقص | مدیران، فعالیت‌ها و آموزش‌های مذهبی | متخصصان منابع انسانی | هماهنگ‌کنندگان آموزشی | مدیران برنامه‌ریزی رسانه | مدیران/کارگردانان فنی رسانه | برنامه‌ریزان جلسات، همایش‌ها و رویدادها | مدیران موسیقی و آهنگسازان | نوازندگان و خوانندگان | شاعران، ترانه‌سرایان و نویسندگان خلاق | تهیه‌کنندگان و کارگردانان | متخصصان روابط عمومی | مدیران آموزش و توسعه | متخصصان آموزش و توسعه | نویسندگان و مؤلفان</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -664,12 +664,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Media Technical Directors/Managers (مدیران/کارگردانان فنی رسانه)</t>
+          <t>مدیران/کارگردانان فنی رسانه (Media Technical Directors/Managers)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Broadcast Director | News Technical Director | Newscast Director | Operations Director | Production Director | Production Manager | Studio Director | Technical Director</t>
+          <t>کارگردان پخش | مدیر فنی اخبار | کارگردان بخش خبری | مدیر عملیات | مدیر تولید | مدیر تولید | مدیر استودیو | مدیر فنی</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -679,27 +679,27 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>صحبت کردن | گوش دادن فعال | نظارت | تفکر انتقادی | درک مطلب | یادگیری فعال | نوشتن | استراتژی‌های یادگیری</t>
+          <t>سخن گفتن | گوش دادن فعال | نظارت | تفکر انتقادی | درک مطلب | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ارتباطات و رسانه | کامپیوتر و الکترونیک | زبان انگلیسی | مخابرات | مهندسی و فناوری | مدیریت و اداره | خدمات مشتری و شخصی</t>
+          <t>ارتباطات و رسانه | رایانه و الکترونیک | زبان انگلیسی | مخابرات | مهندسی و فناوری | مدیریت و اداره | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | دید نزدیک | درک نوشتاری | بیان نوشتاری | استدلال استقرایی | دید دور | تشخیص گفتار | وضوح گفتار | نظم‌دهی اطلاعات | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | خلاقیت | انعطاف‌پذیری بستار | سرعت ادراکی | توجه انتخابی | تشخیص رنگ بصری | اشتراک زمانی | تجسم | سرعت بستار</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | بینایی نزدیک | درک کتبی | بیان کتبی | استدلال استقرایی | بینایی دور | تشخیص گفتار | وضوح گفتار | ترتیب‌دهی اطلاعات | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | اصالت | انعطاف‌پذیری بستار | سرعت ادراکی | توجه انتخابی | تشخیص رنگ بصری | تقسیم توجه | تجسم | سرعت بستار</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>ایمیل | تماس با دیگران | فشار زمانی | محیط داخلی، دارای کنترل محیطی | اهمیت دقیق یا صحیح بودن | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | بحث‌های رودررو با افراد و درون تیم‌ها | تناوب تصمیم‌گیری | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | نتایج کاری و خروجی‌های سایر کارکنان | صرف زمان برای نشستن | اهمیت تکرار وظایف مشابه | صرف زمان برای استفاده از دستان جهت کار با، کنترل یا احساس اشیاء، ابزارها یا کنترل‌ها | مجاورت فیزیکی | موقعیت‌های تعارض</t>
+          <t>ایمیل | ارتباط با دیگران | فشار زمانی | محیط داخلی، دارای کنترل شرایط محیطی | اهمیت دقیق یا درست بودن | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | فراوانی تصمیم‌گیری | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | پیامدهای کاری و نتایج سایر کارکنان | صرف زمان برای نشستن | اهمیت تکرار وظایف یکسان | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | نزدیکی فیزیکی | موقعیت‌های تعارض</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>مدیران هنری | تکنسین‌های صوتی و تصویری | گویندگان پخش و دی‌جی‌های رادیو | تکنسین‌های پخش | اپراتورهای دوربین، تلویزیون، ویدیو و فیلم | معماران شبکه کامپیوتری | متخصصان پشتیبانی شبکه کامپیوتری | تحلیلگران سیستم‌های کامپیوتری | ویراستاران فیلم و ویدیو | سرپرستان خط اول کارکنان سرگرمی و تفریحی، به جز خدمات قمار | مدیران پروژه فناوری اطلاعات | مدیران برنامه‌ریزی رسانه | مدیران شبکه و سیستم‌های کامپیوتری | تهیه‌کنندگان و کارگردانان | متخصصان مدیریت پروژه | متخصصان روابط عمومی | تکنسین‌های مهندسی صدا | هنرمندان جلوه‌های ویژه و انیماتورها | مدیران استعداد | مدیران وب</t>
+          <t>مدیران هنری | تکنسین‌های صوتی و تصویری | گویندگان رادیو و تلویزیون و دی‌جی‌های رادیو | تکنسین‌های پخش | اپراتورهای دوربین، تلویزیون، ویدئو و فیلم | معماران شبکه کامپیوتری | متخصصان پشتیبانی شبکه کامپیوتری | تحلیلگران سیستم‌های کامپیوتری | تدوینگران فیلم و ویدئو | سرپرستان خط اول کارگران سرگرمی و تفریح، به جز خدمات قمار | مدیران پروژه فناوری اطلاعات | مدیران برنامه‌ریزی رسانه | مدیران شبکه و سیستم‌های کامپیوتری | تهیه‌کنندگان و کارگردانان | متخصصان مدیریت پروژه | متخصصان روابط عمومی | تکنسین‌های مهندسی صدا | هنرمندان جلوه‌های ویژه و انیماتورها | مدیران استعداد | مدیران وب</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -721,12 +721,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Athletes and Sports Competitors (ورزشکاران و رقبای ورزشی)</t>
+          <t>ورزشکاران و رقبای ورزشی (Athletes and Sports Competitors)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Baseball Pitcher | Baseball Player | Basketball Player | Golf Professional | Hockey Player | Major League Baseball Player | Minor League Baseball Player | Professional Athlete | Professional Golf Tournament Player | Race Car Driver</t>
+          <t>پرتاب‌کننده بیسبال | بازیکن بیسبال | بازیکن بسکتبال | گلف‌باز حرفه‌ای | بازیکن هاکی | بازیکن لیگ برتر بیسبال | بازیکن لیگ دسته پایین بیسبال | ورزشکار حرفه‌ای | گلف‌باز حرفه‌ای مسابقات | راننده اتومبیل مسابقه‌ای</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>صحبت کردن | گوش دادن فعال | تفکر انتقادی | نظارت | درک مطلب | یادگیری فعال</t>
+          <t>سخن گفتن | گوش دادن فعال | تفکر انتقادی | نظارت | درک مطلب | یادگیری فعال</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -746,17 +746,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | قدرت ایستا | استقامت | قدرت انفجاری | قدرت پویا | وضوح گفتار | دید نزدیک | هماهنگی کلی بدن | استدلال استقرایی | هماهنگی چند اندامی | استدلال قیاسی | انعطاف‌پذیری دامنه | تشخیص گفتار | دید دور | ثبات بازو-دست | قدرت تنه | تعادل کلی بدن | نظم‌دهی اطلاعات | درک نوشتاری | توجه انتخابی | مهارت دستی | تجسم</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | قدرت ایستا | استقامت | قدرت انفجاری | قدرت پویا | وضوح گفتار | بینایی نزدیک | هماهنگی کلی بدن | استدلال استقرایی | هماهنگی چند عضو | استدلال قیاسی | انعطاف‌پذیری دامنه حرکت | تشخیص گفتار | بینایی دور | ثبات دست و بازو | قدرت تنه | تعادل کلی بدن | ترتیب‌دهی اطلاعات | درک کتبی | توجه انتخابی | مهارت دستی | تجسم</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>بحث‌های رودررو با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | سطح رقابت | تماس با دیگران | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فضای باز، در معرض تمام شرایط آب و هوایی | آزادی در تصمیم‌گیری | مکالمات تلفنی | صرف زمان برای ایستادن | ایمیل | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای انجام حرکات تکراری | فشار زمانی | اهمیت دقیق یا صحیح بودن | صرف زمان برای استفاده از دستان جهت کار با، کنترل یا احساس اشیاء، ابزارها یا کنترل‌ها | اهمیت تکرار وظایف مشابه | تناوب تصمیم‌گیری | سلامت و ایمنی سایر کارکنان</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | سطح رقابت | ارتباط با دیگران | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فضای باز، در معرض تمام شرایط آب و هوایی | آزادی در تصمیم‌گیری | مکالمات تلفنی | صرف زمان برای ایستادن | ایمیل | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای انجام حرکات تکراری | فشار زمانی | اهمیت دقیق یا درست بودن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | اهمیت تکرار وظایف یکسان | فراوانی تصمیم‌گیری | سلامت و ایمنی سایر کارکنان</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>ملازمان سرگرمی و تفریحی | مربیان حیوانات | مربیان ورزشی | معلمان آموزش شغلی/فنی، مقطع راهنمایی | معلمان آموزش شغلی/فنی، پس از متوسطه | معلمان آموزش شغلی/فنی، مقطع دبیرستان | مربیان و استعدادیاب‌ها | رقصندگان | مربیان تمرین و تناسب اندام گروهی | هماهنگ‌کنندگان تناسب اندام و سلامتی | مدیران قمار | نویسندگان و دوندگان قمار و کتاب ورزشی | نجات‌غریق‌ها، گشت اسکی و سایر کارکنان خدمات حفاظتی تفریحی | نوازندگان و خوانندگان | کارکنان تفریحی | معلمان غنی‌سازی شخصی | پزشکان طب ورزشی | مدیران آموزش و توسعه | متخصصان آموزش و توسعه | داوران، قضاوت‌کنندگان و سایر مقامات ورزشی</t>
+          <t>متصدیان تفریح و سرگرمی | مربیان حیوانات | مربیان ورزشی | معلمان آموزش‌های شغلی/فنی، دوره راهنمایی | اساتید آموزش‌های شغلی/فنی، پس از متوسطه | معلمان آموزش فنی/حرفه‌ای، دوره متوسطه | مربیان و استعدادیاب‌ها | رقصندگان | مربیان ورزشی و مدرسان تناسب اندام گروهی | هماهنگ‌کنندگان تناسب اندام و سلامتی | مدیران قماربازی | نویسندگان و دوندگان دفاتر شرط‌بندی ورزشی و قمار | نجات‌غریق‌ها، گشت اسکی و سایر کارکنان خدمات حفاظتی تفریحی | نوازندگان و خوانندگان | کارکنان تفریحات | معلمان خودسازی | پزشکان طب ورزشی | مدیران آموزش و توسعه | متخصصان آموزش و توسعه | داوران، قضاوت‌کنندگان و سایر مقامات ورزشی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -778,12 +778,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Coaches and Scouts (مربیان و استعدادیاب‌ها)</t>
+          <t>مربیان و استعدادیاب‌ها (Coaches and Scouts)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Baseball Coach | Basketball Coach | Coach | Cross Country Coach | Football Coach | Gymnastics Coach | Soccer Coach | Softball Coach | Track and Field Coach | Volleyball Coach</t>
+          <t>مربی بیسبال | مربی بسکتبال | مربی | مربی دوی صحرانوردی | مربی فوتبال | مربی ژیمناستیک | مربی فوتبال | مربی سافت‌بال | مربی دو و میدانی | مربی والیبال</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -793,27 +793,27 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>صحبت کردن | استراتژی‌های یادگیری | نظارت | تفکر انتقادی | گوش دادن فعال | درک مطلب | یادگیری فعال | نوشتن</t>
+          <t>سخن گفتن | راهبردهای یادگیری | نظارت | تفکر انتقادی | گوش دادن فعال | درک مطلب | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>آموزش و پرورش | زبان انگلیسی | مدیریت و اداره | روانشناسی | خدمات مشتری و شخصی | ارتباطات و رسانه | پرسنل و منابع انسانی | ایمنی و امنیت عمومی | کامپیوتر و الکترونیک | اداری</t>
+          <t>آموزش و پرورش | زبان انگلیسی | مدیریت و اداره | روان‌شناسی | خدمات مشتری و شخصی | ارتباطات و رسانه | پرسنل و منابع انسانی | ایمنی و امنیت عمومی | رایانه و الکترونیک | اداری</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | تشخیص گفتار | وضوح گفتار | خلاقیت | نظم‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | درک نوشتاری | روانی ایده‌ها | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | دید نزدیک | بیان نوشتاری | تجسم | دید دور | توجه انتخابی | انعطاف‌پذیری بستار</t>
+          <t>بیان شفاهی | درک شفاهی | تشخیص گفتار | وضوح گفتار | اصالت | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | درک کتبی | روانی ایده‌ها | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | بینایی نزدیک | بیان کتبی | تجسم | بینایی دور | توجه انتخابی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>تماس با دیگران | ایمیل | کار با یا مشارکت در یک گروه کاری یا تیم | محیط داخلی، دارای کنترل محیطی | بحث‌های رودررو با افراد و درون تیم‌ها | تعیین وظایف، اولویت‌ها و اهداف | تناوب تصمیم‌گیری | آزادی در تصمیم‌گیری | سخنرانی عمومی | مجاورت فیزیکی | سطح رقابت | صرف زمان برای ایستادن | فشار زمانی | موقعیت‌های تعارض | مکالمات تلفنی | اهمیت دقیق یا صحیح بودن | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری</t>
+          <t>ارتباط با دیگران | ایمیل | کار با یا مشارکت در یک گروه کاری یا تیم | محیط داخلی، دارای کنترل شرایط محیطی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تعیین وظایف، اولویت‌ها و اهداف | فراوانی تصمیم‌گیری | آزادی در تصمیم‌گیری | سخنرانی عمومی | نزدیکی فیزیکی | سطح رقابت | صرف زمان برای ایستادن | فشار زمانی | موقعیت‌های تعارض | مکالمات تلفنی | اهمیت دقیق یا درست بودن | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>ورزشکاران و رقبای ورزشی | مربیان ورزشی | مدیران آموزش، مهدکودک تا دبیرستان | مدیران آموزش، پس از متوسطه | مدیران آموزش و مراقبت از کودک، پیش‌دبستانی و مهدکودک | مشاوران و راهنمایان آموزشی، راهنمایی و شغلی | معلمان مدرسه ابتدایی، به جز آموزش ویژه | مربیان تمرین و تناسب اندام گروهی | هماهنگ‌کنندگان تناسب اندام و سلامتی | هماهنگ‌کنندگان آموزشی | کارکنان تفریحی | معلمان مطالعات تفریحی و تناسب اندام، پس از متوسطه | درمانگران تفریحی | معلمان دبیرستان، به جز آموزش ویژه و شغلی/فنی | معلمان غنی‌سازی شخصی | معلمان آموزش ویژه، دبیرستان | مدیران آموزش و توسعه | متخصصان آموزش و توسعه | معلمان خصوصی | داوران، قضاوت‌کنندگان و سایر مقامات ورزشی</t>
+          <t>ورزشکاران و رقبای ورزشی | مربیان ورزشی | مدیران آموزشی، مهدکودک تا دبیرستان | مدیران آموزشی، پس از متوسطه | مدیران آموزش و مراقبت از کودکان، پیش‌دبستانی و مهدکودک | مشاوران و راهنمایان آموزشی، شغلی و تحصیلی | معلمان دبستان، به استثنای آموزش استثنایی | مربیان ورزشی و مدرسان تناسب اندام گروهی | هماهنگ‌کنندگان تناسب اندام و سلامتی | هماهنگ‌کنندگان آموزشی | کارکنان تفریحات | اساتید مطالعات تفریحی و تناسب اندام، پس از متوسطه | درمانگران تفریحی | معلمان دبیرستان، به استثنای آموزش ویژه و فنی/حرفه‌ای | معلمان خودسازی | معلمان آموزش ویژه، متوسطه | مدیران آموزش و توسعه | متخصصان آموزش و توسعه | معلمان خصوصی | داوران، قضاوت‌کنندگان و سایر مقامات ورزشی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -835,12 +835,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Umpires, Referees, and Other Sports Officials (داوران، قضاوت‌کنندگان و سایر مقامات ورزشی)</t>
+          <t>داوران، قضاوت‌کنندگان و سایر مقامات ورزشی (Umpires, Referees, and Other Sports Officials)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Basketball Referee | Diving Judge | Dressage Judge | Football Referee | Horse Show Judge | Major League Baseball Umpire (MLB Umpire) | Referee | Soccer Referee | Softball Umpire | Sports Official</t>
+          <t>داور بسکتبال | داور شیرجه | داور درساژ | داور فوتبال | داور مسابقات اسب‌سواری | داور لیگ برتر بیسبال (MLB) | داور | داور فوتبال | داور سافت‌بال | مسئول فنی مسابقات ورزشی</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>صحبت کردن | تفکر انتقادی | گوش دادن فعال | نظارت | یادگیری فعال | درک مطلب | استراتژی‌های یادگیری</t>
+          <t>سخن گفتن | تفکر انتقادی | گوش دادن فعال | نظارت | یادگیری فعال | درک مطلب | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -860,17 +860,17 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>بیان شفاهی | دید دور | دید نزدیک | درک شفاهی | حساسیت به مسئله | وضوح گفتار | تشخیص گفتار | استدلال قیاسی | سرعت ادراکی | انعطاف‌پذیری بستار | اشتراک زمانی | توجه انتخابی | قدرت تنه | سرعت بستار | حافظه‌سپاری | استدلال استقرایی | درک نوشتاری</t>
+          <t>بیان شفاهی | بینایی دور | بینایی نزدیک | درک شفاهی | حساسیت به مسئله | وضوح گفتار | تشخیص گفتار | استدلال قیاسی | سرعت ادراکی | انعطاف‌پذیری بستار | تقسیم توجه | توجه انتخابی | قدرت تنه | سرعت بستار | حفظ کردن | استدلال استقرایی | درک کتبی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>آزادی در تصمیم‌گیری | صرف زمان برای ایستادن | کار با یا مشارکت در یک گروه کاری یا تیم | بحث‌های رودررو با افراد و درون تیم‌ها | اهمیت دقیق یا صحیح بودن | تماس با دیگران | مجاورت فیزیکی | ایمیل</t>
+          <t>آزادی در تصمیم‌گیری | صرف زمان برای ایستادن | کار با یا مشارکت در یک گروه کاری یا تیم | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | ارتباط با دیگران | نزدیکی فیزیکی | ایمیل</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ملازمان سرگرمی و تفریحی | مربیان حیوانات | ورزشکاران و رقبای ورزشی | مربیان ورزشی | مأموران قضایی | مربیان و استعدادیاب‌ها | افسران انطباق | مدیران آموزش، مهدکودک تا دبیرستان | مدیران آموزش، پس از متوسطه | مربیان تمرین و تناسب اندام گروهی | سرپرستان خط اول کارکنان سرگرمی و تفریحی، به جز خدمات قمار | سرپرستان خط اول کارکنان آتش‌نشانی و پیشگیری | سرپرستان خط اول پلیس و کارآگاهان | نویسندگان و دوندگان قمار و کتاب ورزشی | نجات‌غریق‌ها، گشت اسکی و سایر کارکنان خدمات حفاظتی تفریحی | برنامه‌ریزان جلسات، کنوانسیون‌ها و رویدادها | افسران گشت پلیس و کلانتر | کارکنان تفریحی | معلمان غنی‌سازی شخصی | متخصصان آموزش و توسعه</t>
+          <t>متصدیان تفریح و سرگرمی | مربیان حیوانات | ورزشکاران و رقبای ورزشی | مربیان ورزشی | ضابطان دادگستری | مربیان و استعدادیاب‌ها | افسران انطباق | مدیران آموزشی، مهدکودک تا دبیرستان | مدیران آموزشی، پس از متوسطه | مربیان ورزشی و مدرسان تناسب اندام گروهی | سرپرستان خط اول کارگران سرگرمی و تفریح، به جز خدمات قمار | سرپرستان خط اول آتش‌نشانی و پیشگیری | سرپرستان خط اول پلیس و کارآگاهان | نویسندگان و دوندگان دفاتر شرط‌بندی ورزشی و قمار | نجات‌غریق‌ها، گشت اسکی و سایر کارکنان خدمات حفاظتی تفریحی | برنامه‌ریزان جلسات، همایش‌ها و رویدادها | ماموران گشت پلیس و کلانتر | کارکنان تفریحات | معلمان خودسازی | متخصصان آموزش و توسعه</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -892,12 +892,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Dancers (رقصندگان)</t>
+          <t>رقصندگان (Dancers)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ballerina | Ballet Company Member | Ballet Dancer | Ballet Soloist | Belly Dancer | Company Dancer | Dancer | Latin Dancer | Performing Artist | Soloist Dancer</t>
+          <t>بالرین | عضو گروه باله | رقصنده باله | تک‌نواز باله | رقصنده شکم | رقصنده گروه هنری | رقصنده | رقصنده لاتین | هنرمند اجرای صحنه | رقصنده تک‌نفره</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -917,17 +917,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>هماهنگی کلی بدن | انعطاف‌پذیری دامنه | قدرت پویا | استقامت | قدرت تنه | تعادل کلی بدن | قدرت ایستا | انعطاف‌پذیری پویا | هماهنگی چند اندامی | درک شفاهی | سرعت حرکت اندام | دید نزدیک | تشخیص گفتار | توجه انتخابی | حساسیت به مسئله | بیان شفاهی</t>
+          <t>هماهنگی کلی بدن | انعطاف‌پذیری دامنه حرکت | قدرت پویا | استقامت | قدرت تنه | تعادل کلی بدن | قدرت ایستا | انعطاف‌پذیری پویا | هماهنگی چند عضو | درک شفاهی | سرعت حرکت اعضا | بینایی نزدیک | تشخیص گفتار | توجه انتخابی | حساسیت به مسئله | بیان شفاهی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>مجاورت فیزیکی | محیط داخلی، دارای کنترل محیطی | تماس با دیگران | بحث‌های رودررو با افراد و درون تیم‌ها | صرف زمان برای خم شدن یا پیچاندن بدن | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای انجام حرکات تکراری | صرف زمان برای ایستادن | صرف زمان برای حفظ یا بازیابی تعادل | سطح رقابت | اهمیت دقیق یا صحیح بودن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت تکرار وظایف مشابه</t>
+          <t>نزدیکی فیزیکی | محیط داخلی، دارای کنترل شرایط محیطی | ارتباط با دیگران | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای خم کردن یا چرخاندن بدن | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای انجام حرکات تکراری | صرف زمان برای ایستادن | صرف زمان برای حفظ یا بازیابی تعادل | سطح رقابت | اهمیت دقیق یا درست بودن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت تکرار وظایف یکسان</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>بازیگران | نمایندگان و مدیران تجاری هنرمندان، مجریان و ورزشکاران | درمانگران هنری | معلمان هنر، نمایش و موسیقی، پس از متوسطه | ورزشکاران و رقبای ورزشی | طراحان رقص | مربیان و استعدادیاب‌ها | ملازمان لباس | هنرمندان صنایع دستی | دی‌جی‌ها، به جز رادیو | مربیان تمرین و تناسب اندام گروهی | هنرمندان زیبا، شامل نقاشان، مجسمه‌سازان و تصویرگران | هنرمندان آرایش، تئاتر و اجرا | مدل‌ها | مدیران موسیقی و آهنگسازان | درمانگران موسیقی | تعمیرکاران و کوک‌کنندگان آلات موسیقی | نوازندگان و خوانندگان | معلمان غنی‌سازی شخصی | مدیران استعداد</t>
+          <t>بازیگران | نمایندگان و مدیران تجاری هنرمندان، اجراکنندگان و ورزشکاران | هنردرمانگران | مدرسان هنر، نمایش و موسیقی، آموزش عالی | ورزشکاران و رقبای ورزشی | طراحان رقص | مربیان و استعدادیاب‌ها | متصدیان لباس | هنرمندان صنایع دستی | دی‌جی‌ها، به جز رادیو | مربیان ورزشی و مدرسان تناسب اندام گروهی | هنرمندان تجسمی، شامل نقاشان، مجسمه‌سازان و تصویرگران | میکاپ آرتیست‌های تئاتر و نمایش | مدل‌ها | مدیران موسیقی و آهنگسازان | موسیقی‌درمانگران | تعمیرکاران و کوک‌کنندگان سازهای موسیقی | نوازندگان و خوانندگان | معلمان خودسازی | مدیران استعداد</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Choreographers (طراحان رقص)</t>
+          <t>طراحان رقص (Choreographers)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ballet Director | Choreographer | Dance Director | Dance Maker | Musical Choreographer | Opera Choreographer</t>
+          <t>مدیر گروه باله | طراح رقص | مدیر گروه رقص | خالق اثر رقص | طراح رقص موزیکال | طراح رقص اپرا</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -964,27 +964,27 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | صحبت کردن | نظارت | استراتژی‌های یادگیری | درک مطلب | تفکر انتقادی | یادگیری فعال | نوشتن</t>
+          <t>گوش دادن فعال | سخن گفتن | نظارت | راهبردهای یادگیری | درک مطلب | تفکر انتقادی | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>هنرهای زیبا | آموزش و پرورش | مدیریت و اداره | تولید و پردازش | ارتباطات و رسانه | طراحی | زبان انگلیسی</t>
+          <t>هنرهای زیبا | آموزش و پرورش | مدیریت و اداره | تولید و فرآوری | ارتباطات و رسانه | طراحی | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>هماهنگی کلی بدن | بیان شفاهی | خلاقیت | تعادل کلی بدن | درک شفاهی | روانی ایده‌ها | قدرت تنه | استقامت | انعطاف‌پذیری دامنه | تجسم | قدرت پویا | درک نوشتاری | حساسیت به مسئله | استدلال قیاسی | هماهنگی چند اندامی | وضوح گفتار | انعطاف‌پذیری پویا | تشخیص گفتار | استدلال استقرایی | نظم‌دهی اطلاعات | توجه انتخابی | دید نزدیک | حافظه‌سپاری | انعطاف‌پذیری دسته‌بندی | بیان نوشتاری</t>
+          <t>هماهنگی کلی بدن | بیان شفاهی | اصالت | تعادل کلی بدن | درک شفاهی | روانی ایده‌ها | قدرت تنه | استقامت | انعطاف‌پذیری دامنه حرکت | تجسم | قدرت پویا | درک کتبی | حساسیت به مسئله | استدلال قیاسی | هماهنگی چند عضو | وضوح گفتار | انعطاف‌پذیری پویا | تشخیص گفتار | استدلال استقرایی | ترتیب‌دهی اطلاعات | توجه انتخابی | بینایی نزدیک | حفظ کردن | انعطاف‌پذیری دسته‌بندی | بیان کتبی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>مجاورت فیزیکی | ایمیل | بحث‌های رودررو با افراد و درون تیم‌ها | تماس با دیگران | صرف زمان برای خم شدن یا پیچاندن بدن | کار با یا مشارکت در یک گروه کاری یا تیم | سطح رقابت | محیط داخلی، دارای کنترل محیطی | صرف زمان برای ایستادن | مکالمات تلفنی | صرف زمان برای انجام حرکات تکراری | نتایج کاری و خروجی‌های سایر کارکنان | صرف زمان برای حفظ یا بازیابی تعادل | آزادی در تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | فشار زمانی | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا صحیح بودن | نامه‌ها و یادداشت‌های کتبی</t>
+          <t>نزدیکی فیزیکی | ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | صرف زمان برای خم کردن یا چرخاندن بدن | کار با یا مشارکت در یک گروه کاری یا تیم | سطح رقابت | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای ایستادن | مکالمات تلفنی | صرف زمان برای انجام حرکات تکراری | پیامدهای کاری و نتایج سایر کارکنان | صرف زمان برای حفظ یا بازیابی تعادل | آزادی در تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فشار زمانی | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | نامه‌ها و یادداشت‌های کتبی</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>بازیگران | مدیران هنری | درمانگران هنری | معلمان هنر، نمایش و موسیقی، پس از متوسطه | مربیان و استعدادیاب‌ها | ملازمان لباس | رقصندگان | هنرمندان زیبا، شامل نقاشان، مجسمه‌سازان و تصویرگران | طراحان گرافیک | هماهنگ‌کنندگان آموزشی | هنرمندان آرایش، تئاتر و اجرا | مدیران موسیقی و آهنگسازان | درمانگران موسیقی | نوازندگان و خوانندگان | شاعران، ترانه‌سرایان و نویسندگان خلاق | تهیه‌کنندگان و کارگردانان | معلمان غنی‌سازی شخصی | طراحان صحنه و نمایشگاه | هنرمندان جلوه‌های ویژه و انیماتورها | مدیران استعداد</t>
+          <t>بازیگران | مدیران هنری | هنردرمانگران | مدرسان هنر، نمایش و موسیقی، آموزش عالی | مربیان و استعدادیاب‌ها | متصدیان لباس | رقصندگان | هنرمندان تجسمی، شامل نقاشان، مجسمه‌سازان و تصویرگران | طراحان گرافیک | هماهنگ‌کنندگان آموزشی | میکاپ آرتیست‌های تئاتر و نمایش | مدیران موسیقی و آهنگسازان | موسیقی‌درمانگران | نوازندگان و خوانندگان | شاعران، ترانه‌سرایان و نویسندگان خلاق | تهیه‌کنندگان و کارگردانان | معلمان خودسازی | طراحان صحنه و نمایشگاه | هنرمندان جلوه‌های ویژه و انیماتورها | مدیران استعداد</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Music Directors and Composers (مدیران موسیقی و آهنگسازان)</t>
+          <t>مدیران موسیقی و آهنگسازان (Music Directors and Composers)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Arranger | Choir Director | Composer | Conductor | Music Composer | Music Director | Music Producer | Orchestra Director | Songwriter</t>
+          <t>تنظیم‌کننده قطعات موسیقی | رهبر گروه کر | آهنگ‌ساز | لوکوموتیوران | آهنگ‌ساز | مدیر موسیقی | تهیه‌کننده موسیقی | رهبر ارکستر | آهنگساز</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1021,27 +1021,27 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | صحبت کردن | درک مطلب | تفکر انتقادی | نوشتن | یادگیری فعال | نظارت</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نگارش | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>هنرهای زیبا | زبان انگلیسی | آموزش و پرورش | کامپیوتر و الکترونیک | خدمات مشتری و شخصی | فلسفه و الهیات</t>
+          <t>هنرهای زیبا | زبان انگلیسی | آموزش و پرورش | رایانه و الکترونیک | خدمات مشتری و شخصی | فلسفه و الهیات</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>حساسیت شنوایی | نظم‌دهی اطلاعات | درک نوشتاری | روانی ایده‌ها | خلاقیت | درک شفاهی | بیان شفاهی | توجه شنیداری | وضوح گفتار | تشخیص گفتار | دید نزدیک | انعطاف‌پذیری دسته‌بندی | استدلال قیاسی | بیان نوشتاری | حساسیت به مسئله | توجه انتخابی | انعطاف‌پذیری بستار | استدلال استقرایی | سرعت بستار | حافظه‌سپاری</t>
+          <t>حساسیت شنوایی | ترتیب‌دهی اطلاعات | درک کتبی | روانی ایده‌ها | اصالت | درک شفاهی | بیان شفاهی | توجه شنیداری | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | انعطاف‌پذیری دسته‌بندی | استدلال قیاسی | بیان کتبی | حساسیت به مسئله | توجه انتخابی | انعطاف‌پذیری بستار | استدلال استقرایی | سرعت بستار | حفظ کردن</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>آزادی در تصمیم‌گیری | ایمیل | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا صحیح بودن | محیط داخلی، دارای کنترل محیطی | بحث‌های رودررو با افراد و درون تیم‌ها | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | تماس با دیگران | تعامل با مشتریان خارجی یا عموم مردم | فشار زمانی | سخنرانی عمومی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | تناوب تصمیم‌گیری | نامه‌ها و یادداشت‌های کتبی | سطح رقابت | نتایج کاری و خروجی‌های سایر کارکنان</t>
+          <t>آزادی در تصمیم‌گیری | ایمیل | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | محیط داخلی، دارای کنترل شرایط محیطی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | تعامل با مشتریان خارجی یا عموم مردم | فشار زمانی | سخنرانی عمومی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فراوانی تصمیم‌گیری | نامه‌ها و یادداشت‌های کتبی | سطح رقابت | پیامدهای کاری و نتایج سایر کارکنان</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>بازیگران | نمایندگان و مدیران تجاری هنرمندان، مجریان و ورزشکاران | مدیران هنری | معلمان هنر، نمایش و موسیقی، پس از متوسطه | گویندگان پخش و دی‌جی‌های رادیو | طراحان رقص | رقصندگان | مدیران، فعالیت‌های مذهبی و آموزش | ویراستاران فیلم و ویدیو | هنرمندان زیبا، شامل نقاشان، مجسمه‌سازان و تصویرگران | مدیران برنامه‌ریزی رسانه | مدیران/کارگردانان فنی رسانه | درمانگران موسیقی | تعمیرکاران و کوک‌کنندگان آلات موسیقی | نوازندگان و خوانندگان | شاعران، ترانه‌سرایان و نویسندگان خلاق | تهیه‌کنندگان و کارگردانان | تکنسین‌های مهندسی صدا | مدیران استعداد | نویسندگان و مؤلفان</t>
+          <t>بازیگران | نمایندگان و مدیران تجاری هنرمندان، اجراکنندگان و ورزشکاران | مدیران هنری | مدرسان هنر، نمایش و موسیقی، آموزش عالی | گویندگان رادیو و تلویزیون و دی‌جی‌های رادیو | طراحان رقص | رقصندگان | مدیران، فعالیت‌ها و آموزش‌های مذهبی | تدوینگران فیلم و ویدئو | هنرمندان تجسمی، شامل نقاشان، مجسمه‌سازان و تصویرگران | مدیران برنامه‌ریزی رسانه | مدیران/کارگردانان فنی رسانه | موسیقی‌درمانگران | تعمیرکاران و کوک‌کنندگان سازهای موسیقی | نوازندگان و خوانندگان | شاعران، ترانه‌سرایان و نویسندگان خلاق | تهیه‌کنندگان و کارگردانان | تکنسین‌های مهندسی صدا | مدیران استعداد | نویسندگان و مؤلفان</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0039_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0039_fa.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>شنیدن فعال | نظارت | تفکر انتقادی | سخن گفتن | درک مطلب | نگارش | یادگیری فعال | استراتژی‌های یادگیری</t>
+          <t>گوش دادن فعال | نظارت | تفکر انتقادی | سخن گفتن | درک مطلب | نگارش | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ارتباطات و رسانه | زبان انگلیسی | مخابرات و ارتباطات از راه دور | رایانه و الکترونیک | مدیریت و امور اداری | خدمات مشتریان و خدمات فردی</t>
+          <t>ارتباطات و رسانه | زبان انگلیسی | مخابرات | رایانه و الکترونیک | مدیریت و اداره | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | استدلال قیاسی | حساسیت به مسئله | وضوح گفتار | درک کتبی | بیان کتبی | ابتکار و اصالت | مرتب‌سازی اطلاعات | دید نزدیک | تشخیص گفتار | استدلال استقرایی | انعطاف‌پذیری طبقه‌بندی | تجسم فضایی | دید دور | روانی و سیالی ایده‌ها | انعطاف‌پذیری در جمع‌بندی | تقسیم زمان و توجه | توجه انتخابی | سرعت جمع‌بندی | سرعت ادراک</t>
+          <t>بیان شفاهی | درک شفاهی | استدلال قیاسی | حساسیت به مسئله | وضوح گفتار | درک کتبی | بیان کتبی | اصالت | ترتیب‌دهی اطلاعات | بینایی نزدیک | تشخیص گفتار | استدلال استقرایی | انعطاف‌پذیری دسته‌بندی | تجسم | بینایی دور | روانی ایده‌ها | انعطاف‌پذیری بستار | تقسیم توجه | توجه انتخابی | سرعت بستار | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>بازیگران | مدیران هنری | تکنسین‌های صوت و تصویر | گویندگان و مجریان رادیو و تلویزیون | تصویربرداران تلویزیون، ویدیو و سینما | ویراستاران | تدوین‌گران فیلم و ویدیو | طراحان گرافیک | مدیران برنامه‌ریزی و پخش رسانه | مدیران فنی رسانه | رهبران ارکستر، مدیران موسیقی و آهنگسازان | تحلیل‌گران خبر، خبرنگاران و روزنامه‌نگاران | شاعران، ترانه‌سرایان و نویسندگان خلاق | متخصصان مدیریت پروژه | کارشناسان روابط عمومی | تکنسین‌های مهندسی صدا | هنرمندان جلوه‌های ویژه و پویانماها | مسئولان انتخاب بازیگر و استعدادیابی | طراحان بازی‌های رایانه‌ای | نویسندگان و پدیدآورندگان</t>
+          <t>بازیگران | مدیران هنری | تکنسین‌های تجهیزات صوتی و تصویری | گویندگان پخش و مجریان رادیویی | تصویربرداران تلویزیون، ویدیو و سینما | ویراستاران | تدوین‌گران فیلم و ویدیو | طراحان گرافیک | مدیران برنامه‌ریزی و پخش رسانه | مدیران فنی رسانه | رهبران ارکستر، مدیران موسیقی و آهنگسازان | تحلیل‌گران خبر، خبرنگاران و روزنامه‌نگاران | شاعران، ترانه‌سرایان و نویسندگان خلاق | کارشناسان مدیریت پروژه | کارشناسان روابط عمومی | تکنسین‌های مهندسی صدا | پویانماها و طراحان جلوه‌های ویژه | مسئولان انتخاب بازیگر و استعدادیابی | طراحان بازی‌های ویدیویی | نویسندگان و پدیدآورندگان</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>سخن گفتن | درک مطلب | تفکر انتقادی | یادگیری فعال | نظارت | شنیدن فعال | نگارش | استراتژی‌های یادگیری</t>
+          <t>سخن گفتن | درک مطلب | تفکر انتقادی | یادگیری فعال | نظارت | گوش دادن فعال | نگارش | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ارتباطات و رسانه | رایانه و الکترونیک | زبان انگلیسی | مدیریت و امور اداری | مخابرات و ارتباطات از راه دور | خدمات مشتریان و خدمات فردی | بازاریابی و فروش | فنی و مهندسی | اداری و دفتری | امور کارکنان و منابع انسانی | آموزش | تولید و فرآوری | ریاضیات</t>
+          <t>ارتباطات و رسانه | رایانه و الکترونیک | زبان انگلیسی | مدیریت و اداره | مخابرات | خدمات مشتری و شخصی | فروش و بازاریابی | مهندسی و فناوری | اداری | پرسنل و منابع انسانی | آموزش و پرورش | تولید و فرآوری | ریاضیات</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | حساسیت به مسئله | روانی و سیالی ایده‌ها | وضوح گفتار | استدلال قیاسی | دید نزدیک | تشخیص گفتار | ابتکار و اصالت | مرتب‌سازی اطلاعات | استدلال استقرایی | انعطاف‌پذیری طبقه‌بندی | توجه انتخابی | دید دور | تقسیم زمان و توجه</t>
+          <t>درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | حساسیت به مسئله | روانی ایده‌ها | وضوح گفتار | استدلال قیاسی | بینایی نزدیک | تشخیص گفتار | اصالت | ترتیب‌دهی اطلاعات | استدلال استقرایی | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | بینایی دور | تقسیم توجه</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>مدیران هنری | گویندگان و مجریان رادیو و تلویزیون | مدیران ارشد اجرایی | مدیران امور مذهبی و آموزش‌های دینی | مسئولان دفاتر و دستیاران اجرایی مدیریت | سرپرستان رده‌اول کارکنان تفریحی و سرگرمی، به‌جز خدمات شرط‌بندی | سرپرستان رده‌اول فروش غیرخرده‌فروشی | سرپرستان رده‌اول کارکنان امور دفتری و اداری | مدیران عمومی و عملیاتی | مدیران پروژه‌های فناوری اطلاعات | هماهنگ‌کنندگان و کارشناسان برنامه‌ریزی آموزشی | کتابداران و متخصصان مجموعه‌های چندرسانه‌ای | تحلیل‌گران مدیریت | مدیران فنی رسانه | تهیه‌کنندگان و کارگردانان | متخصصان مدیریت پروژه | مدیران روابط عمومی | کارشناسان روابط عمومی | مسئولان انتخاب بازیگر و استعدادیابی | مدیران آموزش و بهسازی منابع انسانی</t>
+          <t>مدیران هنری | گویندگان پخش و مجریان رادیویی | مدیران عامل و مدیران ارشد اجرایی | مدیران فعالیت‌ها و آموزش‌های مذهبی | مسئولان دفاتر و دستیاران اجرایی مدیریت | سرپرستان رده‌اول کارکنان مراکز تفریحی و سرگرمی، به‌جز بازی‌های شرط‌بندی | سرپرستان رده‌اول فروشندگان عمده‌فروشی و غیرخرده‌فروشی | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | مدیران کل و مدیران عملیات | مدیران پروژه‌های فناوری اطلاعات | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | کتابداران و کارشناسان مجموعه‌های رسانه‌ای | کارشناسان تحلیل مدیریت و روش‌ها | مدیران فنی رسانه | تهیه‌کنندگان و کارگردانان | کارشناسان مدیریت پروژه | مدیران روابط عمومی | کارشناسان روابط عمومی | مسئولان انتخاب بازیگر و استعدادیابی | مدیران آموزش و بهسازی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | درک مطلب | تفکر انتقادی | نظارت | نگارش | یادگیری فعال</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | نظارت | نگارش | یادگیری فعال</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | خدمات مشتریان و خدمات فردی | ارتباطات و رسانه | امور کارکنان و منابع انسانی | مدیریت و امور اداری | اداری و دفتری | هنرهای زیبا | بازاریابی و فروش</t>
+          <t>زبان انگلیسی | خدمات مشتری و شخصی | ارتباطات و رسانه | پرسنل و منابع انسانی | مدیریت و اداره | اداری | هنرهای زیبا | فروش و بازاریابی</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | درک کتبی | استدلال استقرایی | وضوح گفتار | بیان کتبی | ابتکار و اصالت | استدلال قیاسی | تشخیص گفتار | دید نزدیک | حساسیت به مسئله | روانی و سیالی ایده‌ها | مرتب‌سازی اطلاعات | انعطاف‌پذیری طبقه‌بندی | دید دور</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | استدلال استقرایی | وضوح گفتار | بیان کتبی | اصالت | استدلال قیاسی | تشخیص گفتار | بینایی نزدیک | حساسیت به مسئله | روانی ایده‌ها | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | بینایی دور</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>بازیگران | مدیران تبلیغات و روابط تجاری | نمایندگان و مدیران برنامه‌های هنرمندان و ورزشکاران | مدیران هنری | گویندگان و مجریان رادیو و تلویزیون | طراحان حرکت (کوروگراف‌ها) | مدیران امور مذهبی و آموزش‌های دینی | متخصصان منابع انسانی | هماهنگ‌کنندگان و کارشناسان برنامه‌ریزی آموزشی | مدیران برنامه‌ریزی و پخش رسانه | مدیران فنی رسانه | برنامه‌ریزان همایش‌ها، گردهمایی‌ها و رویدادها | رهبران ارکستر، مدیران موسیقی و آهنگسازان | موسیقی‌دانان و خوانندگان | شاعران، ترانه‌سرایان و نویسندگان خلاق | تهیه‌کنندگان و کارگردانان | کارشناسان روابط عمومی | مدیران آموزش و بهسازی منابع انسانی | کارشناسان آموزش و بهسازی منابع انسانی | نویسندگان و پدیدآورندگان</t>
+          <t>بازیگران | مدیران تبلیغات و روابط ترویجی | مدیران برنامه‌ها و نمایندگان هنرمندان، مجریان و ورزشکاران | مدیران هنری | گویندگان پخش و مجریان رادیویی | طراحان حرکت و کوروگراف‌ها | مدیران فعالیت‌ها و آموزش‌های مذهبی | کارشناسان منابع انسانی | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | مدیران برنامه‌ریزی و پخش رسانه | مدیران فنی رسانه | کارشناسان برنامه‌ریزی و برگزاری همایش‌ها و رویدادها | رهبران ارکستر، مدیران موسیقی و آهنگسازان | نوازندگان و خوانندگان | شاعران، ترانه‌سرایان و نویسندگان خلاق | تهیه‌کنندگان و کارگردانان | کارشناسان روابط عمومی | مدیران آموزش و بهسازی | کارشناسان آموزش و توسعه منابع انسانی | نویسندگان و پدیدآورندگان</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | نظارت | تفکر انتقادی | درک مطلب | یادگیری فعال | نگارش | استراتژی‌های یادگیری</t>
+          <t>سخن گفتن | گوش دادن فعال | نظارت | تفکر انتقادی | درک مطلب | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ارتباطات و رسانه | رایانه و الکترونیک | زبان انگلیسی | مخابرات و ارتباطات از راه دور | فنی و مهندسی | مدیریت و امور اداری | خدمات مشتریان و خدمات فردی</t>
+          <t>ارتباطات و رسانه | رایانه و الکترونیک | زبان انگلیسی | مخابرات | مهندسی و فناوری | مدیریت و اداره | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | دید نزدیک | درک کتبی | بیان کتبی | استدلال استقرایی | دید دور | تشخیص گفتار | وضوح گفتار | مرتب‌سازی اطلاعات | روانی و سیالی ایده‌ها | انعطاف‌پذیری طبقه‌بندی | ابتکار و اصالت | انعطاف‌پذیری در جمع‌بندی | سرعت ادراک | توجه انتخابی | تشخیص رنگ‌ها | تقسیم زمان و توجه | تجسم فضایی | سرعت جمع‌بندی</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | بینایی نزدیک | درک کتبی | بیان کتبی | استدلال استقرایی | بینایی دور | تشخیص گفتار | وضوح گفتار | ترتیب‌دهی اطلاعات | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | اصالت | انعطاف‌پذیری بستار | سرعت ادراکی | توجه انتخابی | تشخیص رنگ بصری | تقسیم توجه | تجسم | سرعت بستار</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>مدیران هنری | تکنسین‌های صوت و تصویر | گویندگان و مجریان رادیو و تلویزیون | تکنسین‌های پخش رادیو و تلویزیون | تصویربرداران تلویزیون، ویدیو و سینما | معماران شبکه‌های رایانه‌ای | متخصصان پشتیبانی شبکه‌های رایانه‌ای | تحلیل‌گران سیستم‌های رایانه‌ای | تدوین‌گران فیلم و ویدیو | سرپرستان رده‌اول کارکنان تفریحی و سرگرمی، به‌جز خدمات شرط‌بندی | مدیران پروژه‌های فناوری اطلاعات | مدیران برنامه‌ریزی و پخش رسانه | مدیران سیستم‌ها و شبکه‌های رایانه‌ای | تهیه‌کنندگان و کارگردانان | متخصصان مدیریت پروژه | کارشناسان روابط عمومی | تکنسین‌های مهندسی صدا | هنرمندان جلوه‌های ویژه و پویانماها | مسئولان انتخاب بازیگر و استعدادیابی | مدیران و پشتیبانان وب</t>
+          <t>مدیران هنری | تکنسین‌های تجهیزات صوتی و تصویری | گویندگان پخش و مجریان رادیویی | تکنسین‌های پخش و اتاق فرمان | تصویربرداران تلویزیون، ویدیو و سینما | معماران شبکه رایانه‌ای | متخصصان پشتیبانی شبکه رایانه‌ای | تحلیل‌گران سیستم‌های کامپیوتری | تدوین‌گران فیلم و ویدیو | سرپرستان رده‌اول کارکنان مراکز تفریحی و سرگرمی، به‌جز بازی‌های شرط‌بندی | مدیران پروژه‌های فناوری اطلاعات | مدیران برنامه‌ریزی و پخش رسانه | مدیران شبکه و سیستم‌های کامپیوتری | تهیه‌کنندگان و کارگردانان | کارشناسان مدیریت پروژه | کارشناسان روابط عمومی | تکنسین‌های مهندسی صدا | پویانماها و طراحان جلوه‌های ویژه | مسئولان انتخاب بازیگر و استعدادیابی | مدیران وب</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | تفکر انتقادی | نظارت | درک مطلب | یادگیری فعال</t>
+          <t>سخن گفتن | گوش دادن فعال | تفکر انتقادی | نظارت | درک مطلب | یادگیری فعال</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>مدیریت و امور اداری | زبان انگلیسی | خدمات مشتریان و خدمات فردی | امور کارکنان و منابع انسانی | ارتباطات و رسانه | آموزش | بازاریابی و فروش | ریاضیات</t>
+          <t>مدیریت و اداره | زبان انگلیسی | خدمات مشتری و شخصی | پرسنل و منابع انسانی | ارتباطات و رسانه | آموزش و پرورش | فروش و بازاریابی | ریاضیات</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | قدرت ایستا | استقامت بدنی | قدرت انفجاری | قدرت پویا | وضوح گفتار | دید نزدیک | هماهنگی حرکتی کل بدن | استدلال استقرایی | هماهنگی چند عضو بدن | استدلال قیاسی | انعطاف‌پذیری حرکتی | تشخیص گفتار | دید دور | ثبات دست و بازو | قدرت تنه | تعادل عمومی بدن | مرتب‌سازی اطلاعات | درک کتبی | توجه انتخابی | چابکی دستی | تجسم فضایی</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | قدرت ایستا | استقامت | قدرت انفجاری | قدرت پویا | وضوح گفتار | بینایی نزدیک | هماهنگی کلی بدن | استدلال استقرایی | هماهنگی چند عضو | استدلال قیاسی | انعطاف‌پذیری دامنه حرکت | تشخیص گفتار | بینایی دور | ثبات دست و بازو | قدرت تنه | تعادل کلی بدن | ترتیب‌دهی اطلاعات | درک کتبی | توجه انتخابی | مهارت دستی | تجسم</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>متصدیان اماکن تفریحی و سرگرمی | مربیان آموزش حیوانات | مربیان و امدادگران ورزشی (اتلتیک ترینرها) | مربیان آموزش فنی و حرفه‌ای دورهٔ اول متوسطه | مربیان آموزش فنی و حرفه‌ای پس از دیپلم | مربیان آموزش فنی و حرفه‌ای دورهٔ دوم متوسطه | مربیان و استعدادیابان ورزشی | رقصندگان | مربیان ورزشی و تمرین‌دهندگان آمادگی جسمانی گروهی | هماهنگ‌کنندگان تناسب اندام و سلامت | مدیران مراکز تفریحی و شرط‌بندی | متصدیان و ثبت‌کنندگان شرط‌بندی‌های ورزشی | نجات‌غریق‌ها، گشت‌های نجات پیست اسکی و سایر خدمات امدادی تفریحی | موسیقی‌دانان و خوانندگان | کارشناسان و مربیان امور تفریحی | معلمان دوره‌های آزاد و مهارت‌آموزی شخصی | پزشکان متخصص پزشکی ورزشی | مدیران آموزش و بهسازی منابع انسانی | کارشناسان آموزش و بهسازی منابع انسانی | داوران و مسئولان مسابقات ورزشی</t>
+          <t>متصدیان اماکن تفریحی و شهربازی | مربیان و رام‌کنندگان حیوانات | مربیان و متخصصان سلامت و توان‌بخشی ورزشی | معلمان آموزش‌های فنی و حرفه‌ای در دوره اول متوسطه | مدرسان آموزش‌های فنی و حرفه‌ای در آموزش عالی | هنرآموزان و معلمان فنی‌وحرفه‌ای و کاردانش دوره دوم متوسطه | مربیان و استعدادیابان ورزشی | هنرمندان رقص و حرکات موزون | مربیان ورزش و آمادگی جسمانی گروهی | مدیران و هماهنگ‌کننده‌های برنامه‌های سلامت و تندرستی | مدیران سالن‌ها و بازی‌های تفریحی دارای مجوز | متصدیان ثبت و پرداخت شرط‌بندی‌های ورزشی و سرگرمی | ناجیان غریق، گشت اسکی و سایر مشاغل خدمات حفاظتی و امدادی تفریحی | نوازندگان و خوانندگان | کارکنان و متصدیان امور تفریحی و اوقات فراغت | مربیان دوره‌های آزاد و مهارت‌آموزی فردی | پزشکان طب ورزشی | مدیران آموزش و بهسازی | کارشناسان آموزش و توسعه منابع انسانی | داوران و مسئولان مسابقات ورزشی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>سخن گفتن | استراتژی‌های یادگیری | نظارت | تفکر انتقادی | شنیدن فعال | درک مطلب | یادگیری فعال | نگارش</t>
+          <t>سخن گفتن | راهبردهای یادگیری | نظارت | تفکر انتقادی | گوش دادن فعال | درک مطلب | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>آموزش | زبان انگلیسی | مدیریت و امور اداری | روان‌شناسی | خدمات مشتریان و خدمات فردی | ارتباطات و رسانه | امور کارکنان و منابع انسانی | ایمنی و امنیت عمومی | رایانه و الکترونیک | اداری و دفتری</t>
+          <t>آموزش و پرورش | زبان انگلیسی | مدیریت و اداره | روان‌شناسی | خدمات مشتری و شخصی | ارتباطات و رسانه | پرسنل و منابع انسانی | ایمنی و امنیت عمومی | رایانه و الکترونیک | اداری</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | تشخیص گفتار | وضوح گفتار | ابتکار و اصالت | مرتب‌سازی اطلاعات | انعطاف‌پذیری طبقه‌بندی | درک کتبی | روانی و سیالی ایده‌ها | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | دید نزدیک | بیان کتبی | تجسم فضایی | دید دور | توجه انتخابی | انعطاف‌پذیری در جمع‌بندی</t>
+          <t>بیان شفاهی | درک شفاهی | تشخیص گفتار | وضوح گفتار | اصالت | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | درک کتبی | روانی ایده‌ها | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | بینایی نزدیک | بیان کتبی | تجسم | بینایی دور | توجه انتخابی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>ورزشکاران و قهرمانان حرفه‌ای | مربیان و امدادگران ورزشی (اتلتیک ترینرها) | مدیران آموزشی دوره‌های ابتدایی و متوسطه | مدیران آموزش عالی و تکمیلی | مدیران مهدهای کودک و مراکز آموزش پیش‌دبستانی | مشاوران تحصیلی، راهنمایی و شغلی | آموزگاران دورهٔ ابتدایی، به‌جز آموزش استثنایی | مربیان ورزشی و تمرین‌دهندگان آمادگی جسمانی گروهی | هماهنگ‌کنندگان تناسب اندام و سلامت | هماهنگ‌کنندگان و کارشناسان برنامه‌ریزی آموزشی | کارشناسان و مربیان امور تفریحی | مدرسان دانشگاهی رشته‌های تربیت بدنی و علوم ورزشی | متخصصان ورزش‌درمانی (تفریح‌درمانی) | دبیران دورهٔ دوم متوسطه، به‌جز آموزش استثنایی و فنی‌حرفه‌ای | معلمان دوره‌های آزاد و مهارت‌آموزی شخصی | معلمان آموزش استثنایی دورهٔ دوم متوسطه | مدیران آموزش و بهسازی منابع انسانی | کارشناسان آموزش و بهسازی منابع انسانی | مدرسان خصوصی و مربیان آموزشی | داوران و مسئولان مسابقات ورزشی</t>
+          <t>ورزشکاران و قهرمانان حرفه‌ای | مربیان و متخصصان سلامت و توان‌بخشی ورزشی | مدیران آموزشی مقاطع ابتدایی و متوسطه | مدیران آموزش عالی | مدیران مراکز آموزشی و مراقبت از کودک، پیش‌دبستانی و مهدکودک | مشاوران تحصیلی، شغلی و هدایت استعدادها | معلمان دوره ابتدایی، به‌جز آموزش استثنایی | مربیان ورزش و آمادگی جسمانی گروهی | مدیران و هماهنگ‌کننده‌های برنامه‌های سلامت و تندرستی | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | کارکنان و متصدیان امور تفریحی و اوقات فراغت | مدرسان علوم ورزشی، تربیت بدنی و اوقات فراغت در آموزش عالی | کارشناسان تفریح‌درمانی | دبیران دوره دوم متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | مربیان دوره‌های آزاد و مهارت‌آموزی فردی | دبیران آموزش استثنایی دوره دوم متوسطه | مدیران آموزش و بهسازی | کارشناسان آموزش و توسعه منابع انسانی | معلمان خصوصی و مدرسان تقویتی | داوران و مسئولان مسابقات ورزشی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>سخن گفتن | تفکر انتقادی | شنیدن فعال | نظارت | یادگیری فعال | درک مطلب | استراتژی‌های یادگیری</t>
+          <t>سخن گفتن | تفکر انتقادی | گوش دادن فعال | نظارت | یادگیری فعال | درک مطلب | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>بیان شفاهی | دید دور | دید نزدیک | درک شفاهی | حساسیت به مسئله | وضوح گفتار | تشخیص گفتار | استدلال قیاسی | سرعت ادراک | انعطاف‌پذیری در جمع‌بندی | تقسیم زمان و توجه | توجه انتخابی | قدرت تنه | سرعت جمع‌بندی | به خاطرسپاری | استدلال استقرایی | درک کتبی</t>
+          <t>بیان شفاهی | بینایی دور | بینایی نزدیک | درک شفاهی | حساسیت به مسئله | وضوح گفتار | تشخیص گفتار | استدلال قیاسی | سرعت ادراکی | انعطاف‌پذیری بستار | تقسیم توجه | توجه انتخابی | قدرت تنه | سرعت بستار | حفظ کردن | استدلال استقرایی | درک کتبی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>متصدیان اماکن تفریحی و سرگرمی | مربیان آموزش حیوانات | ورزشکاران و قهرمانان حرفه‌ای | مربیان و امدادگران ورزشی (اتلتیک ترینرها) | ضابطان قضایی دادگاه | مربیان و استعدادیابان ورزشی | کارشناسان انطباق و بازرسی مقررات | مدیران آموزشی دوره‌های ابتدایی و متوسطه | مدیران آموزش عالی و تکمیلی | مربیان ورزشی و تمرین‌دهندگان آمادگی جسمانی گروهی | سرپرستان رده‌اول کارکنان تفریحی و سرگرمی، به‌جز خدمات شرط‌بندی | سرپرستان رده‌اول کارکنان آتش‌نشانی و پیشگیری از حریق | سرپرستان رده‌اول افسران پلیس و کارآگاهان | متصدیان و ثبت‌کنندگان شرط‌بندی‌های ورزشی | نجات‌غریق‌ها، گشت‌های نجات پیست اسکی و سایر خدمات امدادی تفریحی | برنامه‌ریزان همایش‌ها، گردهمایی‌ها و رویدادها | افسران گشت پلیس و کلانتری | کارشناسان و مربیان امور تفریحی | معلمان دوره‌های آزاد و مهارت‌آموزی شخصی | کارشناسان آموزش و بهسازی منابع انسانی</t>
+          <t>متصدیان اماکن تفریحی و شهربازی | مربیان و رام‌کنندگان حیوانات | ورزشکاران و قهرمانان حرفه‌ای | مربیان و متخصصان سلامت و توان‌بخشی ورزشی | مأموران انتظامات و حفاظت دادگاه | مربیان و استعدادیابان ورزشی | کارشناسان پایش انطباق و بازرسی مقرراتی | مدیران آموزشی مقاطع ابتدایی و متوسطه | مدیران آموزش عالی | مربیان ورزش و آمادگی جسمانی گروهی | سرپرستان رده‌اول کارکنان مراکز تفریحی و سرگرمی، به‌جز بازی‌های شرط‌بندی | سرپرستان رده‌اول آتش‌نشانی و خدمات ایمنی و پیشگیری | سرپرستان رده‌اول پلیس و کارآگاهان | متصدیان ثبت و پرداخت شرط‌بندی‌های ورزشی و سرگرمی | ناجیان غریق، گشت اسکی و سایر مشاغل خدمات حفاظتی و امدادی تفریحی | کارشناسان برنامه‌ریزی و برگزاری همایش‌ها و رویدادها | ماموران گشت پلیس و کلانتری | کارکنان و متصدیان امور تفریحی و اوقات فراغت | مربیان دوره‌های آزاد و مهارت‌آموزی فردی | کارشناسان آموزش و توسعه منابع انسانی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>شنیدن فعال | تفکر انتقادی</t>
+          <t>گوش دادن فعال | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -917,7 +917,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>هماهنگی حرکتی کل بدن | انعطاف‌پذیری حرکتی | قدرت پویا | استقامت بدنی | قدرت تنه | تعادل عمومی بدن | قدرت ایستا | انعطاف‌پذیری پویا | هماهنگی چند عضو بدن | درک شفاهی | سرعت حرکت اندام‌ها | دید نزدیک | تشخیص گفتار | توجه انتخابی | حساسیت به مسئله | بیان شفاهی</t>
+          <t>هماهنگی کلی بدن | انعطاف‌پذیری دامنه حرکت | قدرت پویا | استقامت | قدرت تنه | تعادل کلی بدن | قدرت ایستا | انعطاف‌پذیری پویا | هماهنگی چند عضو | درک شفاهی | سرعت حرکت اعضا | بینایی نزدیک | تشخیص گفتار | توجه انتخابی | حساسیت به مسئله | بیان شفاهی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>بازیگران | نمایندگان و مدیران برنامه‌های هنرمندان و ورزشکاران | هنردرمانگران | استادان و مدرسان دانشگاهی هنر، تئاتر و موسیقی | ورزشکاران و قهرمانان حرفه‌ای | طراحان حرکت (کوروگراف‌ها) | مربیان و استعدادیابان ورزشی | متصدیان لباس نمایش | هنرمندان صنایع دستی | دی‌جی‌ها و مجریان موسیقی، به‌جز رادیو | مربیان ورزشی و تمرین‌دهندگان آمادگی جسمانی گروهی | هنرمندان هنرهای تجسمی شامل نقاشان، مجسمه‌سازان و تصویرگران | چهره‌پردازان و گریمورهای تئاتر و سینما | مانکن‌ها و مدل‌ها | رهبران ارکستر، مدیران موسیقی و آهنگسازان | موسیقی‌درمانگران | تعمیرکاران و کوک‌کنندگان سازهای موسیقی | موسیقی‌دانان و خوانندگان | معلمان دوره‌های آزاد و مهارت‌آموزی شخصی | مسئولان انتخاب بازیگر و استعدادیابی</t>
+          <t>بازیگران | مدیران برنامه‌ها و نمایندگان هنرمندان، مجریان و ورزشکاران | هنر‌درمانگران | مدرسان هنرهای تجسمی، نمایشی و موسیقی در دانشگاه‌ها و مراکز آموزش عالی | ورزشکاران و قهرمانان حرفه‌ای | طراحان حرکت و کوروگراف‌ها | مربیان و استعدادیابان ورزشی | متصدیان و جامه داران لباس صحنه | هنرمندان صنایع دستی | دی‌جی‌ها (به‌جز رادیو) | مربیان ورزش و آمادگی جسمانی گروهی | هنرمندان هنرهای تجسمی، شامل نقاشان، مجسمه‌سازان و تصویرگران | چهره‌پردازان و گریموران تئاتر و سینما | مدل‌ها | رهبران ارکستر، مدیران موسیقی و آهنگسازان | موسیقی‌درمانگران | تعمیرکاران و کوک‌کنندگان سازهای موسیقی | نوازندگان و خوانندگان | مربیان دوره‌های آزاد و مهارت‌آموزی فردی | مسئولان انتخاب بازیگر و استعدادیابی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | نظارت | استراتژی‌های یادگیری | درک مطلب | تفکر انتقادی | یادگیری فعال | نگارش</t>
+          <t>گوش دادن فعال | سخن گفتن | نظارت | راهبردهای یادگیری | درک مطلب | تفکر انتقادی | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>هنرهای زیبا | آموزش | مدیریت و امور اداری | تولید و فرآوری | ارتباطات و رسانه | طراحی | زبان انگلیسی</t>
+          <t>هنرهای زیبا | آموزش و پرورش | مدیریت و اداره | تولید و فرآوری | ارتباطات و رسانه | طراحی | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>هماهنگی حرکتی کل بدن | بیان شفاهی | ابتکار و اصالت | تعادل عمومی بدن | درک شفاهی | روانی و سیالی ایده‌ها | قدرت تنه | استقامت بدنی | انعطاف‌پذیری حرکتی | تجسم فضایی | قدرت پویا | درک کتبی | حساسیت به مسئله | استدلال قیاسی | هماهنگی چند عضو بدن | وضوح گفتار | انعطاف‌پذیری پویا | تشخیص گفتار | استدلال استقرایی | مرتب‌سازی اطلاعات | توجه انتخابی | دید نزدیک | به خاطرسپاری | انعطاف‌پذیری طبقه‌بندی | بیان کتبی</t>
+          <t>هماهنگی کلی بدن | بیان شفاهی | اصالت | تعادل کلی بدن | درک شفاهی | روانی ایده‌ها | قدرت تنه | استقامت | انعطاف‌پذیری دامنه حرکت | تجسم | قدرت پویا | درک کتبی | حساسیت به مسئله | استدلال قیاسی | هماهنگی چند عضو | وضوح گفتار | انعطاف‌پذیری پویا | تشخیص گفتار | استدلال استقرایی | ترتیب‌دهی اطلاعات | توجه انتخابی | بینایی نزدیک | حفظ کردن | انعطاف‌پذیری دسته‌بندی | بیان کتبی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>بازیگران | مدیران هنری | هنردرمانگران | استادان و مدرسان دانشگاهی هنر، تئاتر و موسیقی | مربیان و استعدادیابان ورزشی | متصدیان لباس نمایش | رقصندگان | هنرمندان هنرهای تجسمی شامل نقاشان، مجسمه‌سازان و تصویرگران | طراحان گرافیک | هماهنگ‌کنندگان و کارشناسان برنامه‌ریزی آموزشی | چهره‌پردازان و گریمورهای تئاتر و سینما | رهبران ارکستر، مدیران موسیقی و آهنگسازان | موسیقی‌درمانگران | موسیقی‌دانان و خوانندگان | شاعران، ترانه‌سرایان و نویسندگان خلاق | تهیه‌کنندگان و کارگردانان | معلمان دوره‌های آزاد و مهارت‌آموزی شخصی | طراحان صحنه و نمایشگاه | هنرمندان جلوه‌های ویژه و پویانماها | مسئولان انتخاب بازیگر و استعدادیابی</t>
+          <t>بازیگران | مدیران هنری | هنر‌درمانگران | مدرسان هنرهای تجسمی، نمایشی و موسیقی در دانشگاه‌ها و مراکز آموزش عالی | مربیان و استعدادیابان ورزشی | متصدیان و جامه داران لباس صحنه | هنرمندان رقص و حرکات موزون | هنرمندان هنرهای تجسمی، شامل نقاشان، مجسمه‌سازان و تصویرگران | طراحان گرافیک | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | چهره‌پردازان و گریموران تئاتر و سینما | رهبران ارکستر، مدیران موسیقی و آهنگسازان | موسیقی‌درمانگران | نوازندگان و خوانندگان | شاعران، ترانه‌سرایان و نویسندگان خلاق | تهیه‌کنندگان و کارگردانان | مربیان دوره‌های آزاد و مهارت‌آموزی فردی | طراحان صحنه و نمایشگاه | پویانماها و طراحان جلوه‌های ویژه | مسئولان انتخاب بازیگر و استعدادیابی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نگارش | یادگیری فعال | نظارت</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نگارش | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>هنرهای زیبا | زبان انگلیسی | آموزش | رایانه و الکترونیک | خدمات مشتریان و خدمات فردی | فلسفه و الهیات</t>
+          <t>هنرهای زیبا | زبان انگلیسی | آموزش و پرورش | رایانه و الکترونیک | خدمات مشتری و شخصی | فلسفه و الهیات</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>حساسیت شنیداری | مرتب‌سازی اطلاعات | درک کتبی | روانی و سیالی ایده‌ها | ابتکار و اصالت | درک شفاهی | بیان شفاهی | توجه شنوایی | وضوح گفتار | تشخیص گفتار | دید نزدیک | انعطاف‌پذیری طبقه‌بندی | استدلال قیاسی | بیان کتبی | حساسیت به مسئله | توجه انتخابی | انعطاف‌پذیری در جمع‌بندی | استدلال استقرایی | سرعت جمع‌بندی | به خاطرسپاری</t>
+          <t>حساسیت شنوایی | ترتیب‌دهی اطلاعات | درک کتبی | روانی ایده‌ها | اصالت | درک شفاهی | بیان شفاهی | توجه شنیداری | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | انعطاف‌پذیری دسته‌بندی | استدلال قیاسی | بیان کتبی | حساسیت به مسئله | توجه انتخابی | انعطاف‌پذیری بستار | استدلال استقرایی | سرعت بستار | حفظ کردن</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>بازیگران | نمایندگان و مدیران برنامه‌های هنرمندان و ورزشکاران | مدیران هنری | استادان و مدرسان دانشگاهی هنر، تئاتر و موسیقی | گویندگان و مجریان رادیو و تلویزیون | طراحان حرکت (کوروگراف‌ها) | رقصندگان | مدیران امور مذهبی و آموزش‌های دینی | تدوین‌گران فیلم و ویدیو | هنرمندان هنرهای تجسمی شامل نقاشان، مجسمه‌سازان و تصویرگران | مدیران برنامه‌ریزی و پخش رسانه | مدیران فنی رسانه | موسیقی‌درمانگران | تعمیرکاران و کوک‌کنندگان سازهای موسیقی | موسیقی‌دانان و خوانندگان | شاعران، ترانه‌سرایان و نویسندگان خلاق | تهیه‌کنندگان و کارگردانان | تکنسین‌های مهندسی صدا | مسئولان انتخاب بازیگر و استعدادیابی | نویسندگان و پدیدآورندگان</t>
+          <t>بازیگران | مدیران برنامه‌ها و نمایندگان هنرمندان، مجریان و ورزشکاران | مدیران هنری | مدرسان هنرهای تجسمی، نمایشی و موسیقی در دانشگاه‌ها و مراکز آموزش عالی | گویندگان پخش و مجریان رادیویی | طراحان حرکت و کوروگراف‌ها | هنرمندان رقص و حرکات موزون | مدیران فعالیت‌ها و آموزش‌های مذهبی | تدوین‌گران فیلم و ویدیو | هنرمندان هنرهای تجسمی، شامل نقاشان، مجسمه‌سازان و تصویرگران | مدیران برنامه‌ریزی و پخش رسانه | مدیران فنی رسانه | موسیقی‌درمانگران | تعمیرکاران و کوک‌کنندگان سازهای موسیقی | نوازندگان و خوانندگان | شاعران، ترانه‌سرایان و نویسندگان خلاق | تهیه‌کنندگان و کارگردانان | تکنسین‌های مهندسی صدا | مسئولان انتخاب بازیگر و استعدادیابی | نویسندگان و پدیدآورندگان</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
